--- a/artfynd/A 2482-2026 artfynd.xlsx
+++ b/artfynd/A 2482-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>75235242</v>
+        <v>65351734</v>
       </c>
       <c r="B2" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,14 +706,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vallåsen, höjder öst om, Hls</t>
+          <t>Vallåsen, höjd Ö om, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596507.0366527946</v>
+        <v>596570</v>
       </c>
       <c r="R2" t="n">
-        <v>6846630.839414488</v>
+        <v>6846909</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-05-28</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-03-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-05-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-03-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,15 +759,15 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>äldre barrblandskog</t>
+          <t>gammal kantskog mellan olikåldrig hällmarkstallskog och medelålders talldominerad prouktionsskog</t>
         </is>
       </c>
       <c r="AN2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>10 substratenheter # torrgrenar på 150-åriga granar</t>
+          <t>5 substratenheter # senvuxna grannar</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,6 +782,116 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>75235242</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79359</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>185</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Vallåsen, höjder öst om, Hls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>596507</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6846631</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Forsa</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2018-05-28</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2018-05-28</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>10 substratenheter # torrgrenar på 150-åriga granar</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
